--- a/results/Int Task Remove ACC -0.6/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC -0.6/Rando_5_permute.xlsx
@@ -440,147 +440,147 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.645151889717</v>
+        <v>0.6193402110040855</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.644896370358065</v>
+        <v>0.6209285840989529</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6532940176090145</v>
+        <v>0.621244639724743</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6526914705807821</v>
+        <v>0.6031354970590637</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6547155640149904</v>
+        <v>0.6025033858074834</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6552346976987772</v>
+        <v>0.6399943405629591</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6562958421439411</v>
+        <v>0.638081816876385</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6312602242939078</v>
+        <v>0.645365878381232</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6084545935763982</v>
+        <v>0.6439133599317489</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6084545935763982</v>
+        <v>0.6439133599317489</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5969502391886451</v>
+        <v>0.6430405114329075</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5969502391886451</v>
+        <v>0.6525369623182856</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.600479292373275</v>
+        <v>0.6496899980008954</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.602616363375277</v>
+        <v>0.6589752758623603</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6011275935566887</v>
+        <v>0.6589752758623603</v>
       </c>
     </row>
     <row r="17">
@@ -590,207 +590,207 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5932423928437686</v>
+        <v>0.6623631950760083</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5887503906700943</v>
+        <v>0.6568691769038656</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5993537401558175</v>
+        <v>0.6688778828637314</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6018445259728742</v>
+        <v>0.6073846502552378</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5872415594142342</v>
+        <v>0.6142625556440918</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5802439893118294</v>
+        <v>0.6159558113408361</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.575751987138155</v>
+        <v>0.6317652797761003</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5724717661667028</v>
+        <v>0.6191473396422447</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.568017423182293</v>
+        <v>0.6235721184033067</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.568017423182293</v>
+        <v>0.6293593151236488</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5640149904690576</v>
+        <v>0.6206537072128258</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5688459253461126</v>
+        <v>0.6036877145165969</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5622692934713748</v>
+        <v>0.617630413420468</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5944330567435994</v>
+        <v>0.6017846936160987</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5900149651282947</v>
+        <v>0.5718776660594269</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.598826863461154</v>
+        <v>0.5721560624959525</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5781083261299869</v>
+        <v>0.5620208132132369</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.578679901114712</v>
+        <v>0.5694058858145226</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5756928586914594</v>
+        <v>0.5691651485672614</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5457428926199251</v>
+        <v>0.5636644432493616</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5457428926199251</v>
+        <v>0.5588750390670094</v>
       </c>
     </row>
     <row r="38">
@@ -800,457 +800,457 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5500332245557624</v>
+        <v>0.5522811613953187</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5439151900979562</v>
+        <v>0.5443878657164819</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5486574323049677</v>
+        <v>0.5271030017541439</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5717671521769123</v>
+        <v>0.5402724554354529</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5758529982345935</v>
+        <v>0.5712054319333031</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5868558166905526</v>
+        <v>0.5712054319333031</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5869983584816941</v>
+        <v>0.5618877742081716</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6155795714032306</v>
+        <v>0.5671586528850459</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5989430086243063</v>
+        <v>0.531909651733449</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6016879059801385</v>
+        <v>0.5140373748095923</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.603821105476702</v>
+        <v>0.5112910696336007</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5961161057441878</v>
+        <v>0.4816480083568205</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5661636759873747</v>
+        <v>0.4934979825937116</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5328367013084281</v>
+        <v>0.4843094923682069</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5548247404683536</v>
+        <v>0.4915625818295467</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5299749548793639</v>
+        <v>0.5230389769089338</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5299749548793639</v>
+        <v>0.5230389769089338</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5293576257394575</v>
+        <v>0.5239347024853657</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5293576257394575</v>
+        <v>0.6019462409793923</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5303677367038425</v>
+        <v>0.6105135305595522</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5289004361426853</v>
+        <v>0.6027223018422735</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5190988402377527</v>
+        <v>0.6127026909074527</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5194148958635428</v>
+        <v>0.5988138411246794</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5179475953023857</v>
+        <v>0.6054548807717106</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5192480691746514</v>
+        <v>0.6204534447951482</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4891907568159613</v>
+        <v>0.6204534447951482</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4887092823214391</v>
+        <v>0.6150590298992846</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.488227807826917</v>
+        <v>0.6208219417218767</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4891383155150228</v>
+        <v>0.6208219417218767</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4808226737883596</v>
+        <v>0.6152163538020999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4838325932892029</v>
+        <v>0.6053595009559098</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4943310601730493</v>
+        <v>0.6159371577237238</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4946094566095749</v>
+        <v>0.6109098319344293</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4946094566095749</v>
+        <v>0.6049948755346197</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4992239391371189</v>
+        <v>0.6129620817718262</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4971326222902981</v>
+        <v>0.6256701223958847</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.49771229224094</v>
+        <v>0.5842383270591481</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4970801809893597</v>
+        <v>0.5849981979901959</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4961320141119893</v>
+        <v>0.5862852975709471</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4975616554838819</v>
+        <v>0.5773431758733412</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4987048054533322</v>
+        <v>0.564873056856225</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4986819283757415</v>
+        <v>0.5241441157340797</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4976060018189037</v>
+        <v>0.5092127751232547</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4973504824599687</v>
+        <v>0.4812953494068853</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4949726742107056</v>
+        <v>0.4997057655866809</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4949726742107056</v>
+        <v>0.5262164270087482</v>
       </c>
     </row>
     <row r="84">
@@ -1260,67 +1260,67 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4949726742107056</v>
+        <v>0.5262164270087482</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4955671262730214</v>
+        <v>0.5212267604087184</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4956572267632244</v>
+        <v>0.5255199079848744</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4951609701570283</v>
+        <v>0.5257983044214</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4927831619077653</v>
+        <v>0.5175713553647803</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4934152731593456</v>
+        <v>0.5085859431972722</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4981561075461977</v>
+        <v>0.5026562046857885</v>
       </c>
     </row>
   </sheetData>
